--- a/AAII_Financials/Quarterly/ADBE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ADBE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>ADBE</t>
   </si>
@@ -656,517 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46262</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46171</v>
+      </c>
+      <c r="F7" s="2">
         <v>46080</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45989</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45898</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45807</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45625</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45534</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45352</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45261</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45170</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45079</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44988</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44897</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44806</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44715</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44624</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44533</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44442</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44351</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44260</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44162</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44071</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43980</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43889</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43798</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43707</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43616</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43525</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43434</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43343</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43252</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43161</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43070</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42979</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42888</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42797</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42706</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6760000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6618000</v>
+      </c>
+      <c r="F8" s="3">
         <v>6398000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6194000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>5988000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>5873000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5714000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5606000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5408000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>5309000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5182000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5048000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4890000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4816000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4655000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4525000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4433000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4386000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4262000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4110000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3935000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3835000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3905000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3424000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3225000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3128000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3091000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2991900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2834100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2744300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2600900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>2464600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>2291100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>2195400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>2078900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>2006600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>1841100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>1772200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>1681600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>1608400</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>763000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>715000</v>
+      </c>
+      <c r="F9" s="3">
         <v>664000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>649000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>642000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>638000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>622000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>616000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>554000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>598000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>590000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>634000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>580000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>572000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>568000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>568000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>546000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>539000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>512000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>507000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>467000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>444000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>447000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>428000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>427000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>415000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>452000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>452000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>416000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>407500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>397300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>359300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>295500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>281300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>258900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>270900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>262900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>239400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>237300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>216600</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5997000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5903000</v>
+      </c>
+      <c r="F10" s="3">
         <v>5734000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>5545000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5346000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>5235000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>5092000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>4990000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4854000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4711000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>4592000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>4414000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4310000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>4244000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>4087000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3957000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>3887000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3847000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>3750000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>3603000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3468000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3391000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3458000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2996000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2798000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2713000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2639000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2539900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2418100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>2336800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2203600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>2105300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1995600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1914100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1820000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1735700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1578200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1532800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>1444300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>1391800</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,127 +1234,135 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1288000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1198000</v>
+      </c>
+      <c r="F12" s="3">
         <v>1110000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1098000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1088000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1082000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1026000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>999000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1022000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>984000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>939000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>889000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>881000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>876000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>827000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>773000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>775000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>738000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>701000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>657000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>651000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>612000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>620000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>558000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>566000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>532000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>532000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>499800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>489800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>476000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>464600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>416000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>399000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>374100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>348800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>324000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>315600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>299400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>285100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AQ12" s="3">
         <v>257800</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1446,62 +1480,68 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>82000</v>
+      </c>
+      <c r="F14" s="3">
         <v>57000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-11000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-23000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>65000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-12000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-4000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>982000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-6000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-5000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1544,11 +1584,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>10</v>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>10</v>
@@ -1562,40 +1602,46 @@
       <c r="AN14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AO14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="E15" s="3">
         <v>37000</v>
       </c>
       <c r="F15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="G15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="H15" s="3">
         <v>38000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>41000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>41000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>42000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>43000</v>
       </c>
       <c r="K15" s="3">
         <v>42000</v>
       </c>
       <c r="L15" s="3">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="M15" s="3">
         <v>42000</v>
@@ -1613,79 +1659,85 @@
         <v>42000</v>
       </c>
       <c r="R15" s="3">
-        <v>43000</v>
+        <v>42000</v>
       </c>
       <c r="S15" s="3">
         <v>42000</v>
       </c>
       <c r="T15" s="3">
+        <v>43000</v>
+      </c>
+      <c r="U15" s="3">
         <v>42000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="W15" s="3">
         <v>40000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>43000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>44000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>45000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>39000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>41000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>40000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>42000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>42700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>43000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>43000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>46600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>32900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>23900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>17100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>18700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>19400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>19300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>19100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AQ15" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1724,246 +1776,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4406000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4280000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3918000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3933000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3815000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3764000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3551000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3571000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3416000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3424000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3275000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3305000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3193000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3192000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3069000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3020000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2949000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2857000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2682000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2609000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2494000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2429000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2451000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2209000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2156000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2112000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2154000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2022000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1980300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1994700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1906100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1744100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>1572500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1496900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1376200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>1357300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>1295400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1268100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>1212600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>1136100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2354000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2338000</v>
+      </c>
+      <c r="F18" s="3">
         <v>2480000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2261000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2173000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>2109000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2163000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>2035000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1992000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1885000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1907000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1743000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1697000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1624000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1586000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1505000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1484000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1529000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1580000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1501000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1441000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1406000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1454000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1215000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1069000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1016000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>937000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>969900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>853800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>749600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>694800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>720500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>718600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>698500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>702700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>649300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>545700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>504100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>469000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>472300</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2005,293 +2071,307 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>206000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-58000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-58000</v>
       </c>
       <c r="H20" s="3">
         <v>5000</v>
       </c>
       <c r="I20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K20" s="3">
         <v>270000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-89000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-82000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-70000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>173000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-67000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-47000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-43000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>40000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-9000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-9000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>8000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>9000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>9000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>19000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>12000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>15000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>23800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>20200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>48100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>6600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>3800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>19700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>12800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>14500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>6900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>9800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2391000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2366000</v>
+      </c>
+      <c r="F21" s="3">
         <v>2514000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2092000</v>
       </c>
-      <c r="F21" s="3">
-        <v>2269000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2208000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2206000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2152000</v>
+      </c>
+      <c r="J21" s="3">
         <v>2199000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1807000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2124000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2009000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2019000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1612000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1806000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1713000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1671000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1760000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1700000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1732000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1784000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1701000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1638000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1608000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1659000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1414000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1279000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1216000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1140000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1289300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1024600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>897000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>887800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>833800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>809400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>787500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>798900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>743400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>642500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>592600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>559600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>556100</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>65000</v>
+      </c>
+      <c r="F22" s="3">
         <v>63000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>66000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>67000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>68000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>62000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>50000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>51000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>41000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>27000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>28000</v>
       </c>
       <c r="N22" s="3">
         <v>27000</v>
       </c>
       <c r="O22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>26000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>32000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>28000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>28000</v>
       </c>
       <c r="S22" s="3">
         <v>28000</v>
@@ -2303,305 +2383,323 @@
         <v>28000</v>
       </c>
       <c r="V22" s="3">
-        <v>27000</v>
+        <v>28000</v>
       </c>
       <c r="W22" s="3">
         <v>28000</v>
       </c>
       <c r="X22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>30000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>27000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>28000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>28000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>33000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>36500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>39500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>40600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>40600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>27900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>21100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>19900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>19100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>18800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>18300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>18100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2357000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2238000</v>
+      </c>
+      <c r="F23" s="3">
         <v>2422000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2264000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2187000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2101000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2182000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1991000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2042000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1930000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>968000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1808000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1743000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1650000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1598000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1517000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1456000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1492000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1543000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1468000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1418000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1386000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1433000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1197000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1060000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1000000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>919000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>957100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>834500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>710800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>702300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>699200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>701400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>690800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>702500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>643000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>541400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>492600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>460600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>456700</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>530000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>526000</v>
+      </c>
+      <c r="F24" s="3">
         <v>533000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>408000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>415000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>410000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>371000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>308000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>358000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>357000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>348000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>325000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>340000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>355000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>351000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>341000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>320000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>314000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>277000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>235000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>206000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>270000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>172000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-1053000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>105000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-100000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>102300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>41700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>78200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>28100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>15000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>11100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-8600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>141500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>121800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>118200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>62200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>57100</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2719,246 +2817,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1712000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1889000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1856000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1772000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1691000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1811000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1683000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1684000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1573000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>620000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1483000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1403000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1295000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1247000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1176000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1136000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1178000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1266000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1233000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1212000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1116000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>2250000</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>955000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>1100000</v>
       </c>
       <c r="AB26" s="3">
         <v>955000</v>
       </c>
       <c r="AC26" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>955000</v>
+      </c>
+      <c r="AE26" s="3">
         <v>854800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>792800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>632600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>674200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>684200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>690300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>691200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>711100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>501500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>419600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>374400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>398400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>399600</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1712000</v>
+      </c>
+      <c r="F27" s="3">
         <v>1889000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1856000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1772000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1691000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1811000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1683000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1684000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1573000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>620000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1483000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1403000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1295000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1247000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1176000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1136000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1178000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1266000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1233000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1212000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1116000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>2250000</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>955000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>1100000</v>
       </c>
       <c r="AB27" s="3">
         <v>955000</v>
       </c>
       <c r="AC27" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>955000</v>
+      </c>
+      <c r="AE27" s="3">
         <v>854800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>792800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>632600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>674200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>684200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>690300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>691200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>711100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>501500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>419600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>374400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>398400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>399600</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3076,8 +3192,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3138,53 +3260,53 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>10</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
-        <v>-3000</v>
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
+      <c r="AE29" s="3">
+        <v>-3000</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>-24000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AK29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AL29" s="3">
         <v>-128000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3195,8 +3317,14 @@
       <c r="AO29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3314,8 +3442,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3433,246 +3567,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-206000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>58000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>58000</v>
       </c>
       <c r="H32" s="3">
         <v>-5000</v>
       </c>
       <c r="I32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-270000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>89000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>82000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>70000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-173000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>67000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>47000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>43000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-40000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>9000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>9000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-8000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-23800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-20200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-48100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-6600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-12600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-19700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-12800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-14500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-6900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1712000</v>
+      </c>
+      <c r="F33" s="3">
         <v>1889000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1856000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1772000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1691000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1811000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1683000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1684000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1573000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>620000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1483000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1403000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1295000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1247000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1176000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1136000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1178000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1266000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1233000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1212000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1116000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>2250000</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>955000</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>1100000</v>
       </c>
       <c r="AB33" s="3">
         <v>955000</v>
       </c>
       <c r="AC33" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>955000</v>
+      </c>
+      <c r="AE33" s="3">
         <v>851900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>792800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>632600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>674200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>678200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>666300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>663200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>583100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>501500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>419600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>374400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>398400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>399600</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3790,251 +3942,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1712000</v>
+      </c>
+      <c r="F35" s="3">
         <v>1889000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1856000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1772000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1691000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1811000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1683000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1684000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1573000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>620000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1483000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1403000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1295000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1247000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1176000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1136000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1178000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1266000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1233000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1212000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1116000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>2250000</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>955000</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>1100000</v>
       </c>
       <c r="AB35" s="3">
         <v>955000</v>
       </c>
       <c r="AC35" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>955000</v>
+      </c>
+      <c r="AE35" s="3">
         <v>851900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>792800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>632600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>674200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>678200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>666300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>663200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>583100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>501500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>419600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>374400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>398400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>399600</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46262</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46171</v>
+      </c>
+      <c r="F38" s="2">
         <v>46080</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45989</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45898</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45807</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45625</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45534</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45352</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45261</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45170</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45079</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44988</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44897</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44806</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44715</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44624</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44533</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44442</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44351</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44260</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44162</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44071</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43980</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43889</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43798</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43707</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43616</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43525</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43434</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43343</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43252</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43161</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43070</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42979</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42888</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42797</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42706</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4076,8 +4246,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4119,365 +4291,385 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4359000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4919000</v>
+      </c>
+      <c r="F41" s="3">
         <v>6332000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5431000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4982000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4931000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6758000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7613000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7193000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7660000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6254000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7141000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6601000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5456000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4072000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4236000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3870000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3365000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2739000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3844000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4623000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4250000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3452000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4478000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3767000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3044000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2688000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2650200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2209000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2082900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1738800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1642800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>1747100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2988000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>2667000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>2306100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>1774600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>1317000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>1068900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>1011300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1283000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>707000</v>
+      </c>
+      <c r="F42" s="3">
         <v>567000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1166000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>963000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>782000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>678000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>273000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>322000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>405000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>566000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>701000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>915000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1145000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1581000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1860000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1894000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1934000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1962000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1954000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1541000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1518000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1511000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1514000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1497000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1307000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1483000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1526800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1441700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1396100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>1487400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>1586200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>3197300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>3346100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>3481000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>3513700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>3593900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>3614600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>3578700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>3750000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2081000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1993000</v>
+      </c>
+      <c r="F43" s="3">
         <v>2092000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2344000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2093000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1735000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1973000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2072000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1802000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1612000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2057000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2224000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1851000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1685000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1801000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2065000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1723000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1588000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1685000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1878000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1545000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1477000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1520000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1479000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1395000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1442000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1465000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1598700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1447900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1314200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1390000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1315600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>1044500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>1074900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>1062700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>1218000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>1006200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>901500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>850800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>833000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4520,11 +4712,11 @@
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -4595,269 +4787,287 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>69000</v>
+      </c>
+      <c r="F45" s="3">
         <v>44000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>319000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>16000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>13000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>159000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>358000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>9000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>51000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>52000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>286000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>82000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>67000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>46000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>835000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1002000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1021000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1090000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>993000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>910000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>833000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>901000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>675000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>728000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>856000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>819000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>719200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>651400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>549500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>517400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>312500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>311900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>332500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>270200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>210100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>206400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>219200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>257100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>245400</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9158000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9068000</v>
+      </c>
+      <c r="F46" s="3">
         <v>10386000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10163000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9412000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8978000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10855000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11232000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10716000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11023000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>10008000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>11084000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>10410000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>9274000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>8342000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>8996000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>8489000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>7908000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7476000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>8669000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>8619000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8078000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>7384000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>8146000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>7387000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>6649000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>6455000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>6494900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>5750100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>5342600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>5133700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>4857000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>6300900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>7741400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>7480800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>7247800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>6581100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>6052200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>5755600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>5839800</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>35000</v>
+      </c>
+      <c r="F47" s="3">
         <v>107000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>92000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>92000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>63000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>35000</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>10</v>
@@ -4877,11 +5087,11 @@
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4947,251 +5157,269 @@
         <v>0</v>
       </c>
       <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
         <v>80400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AQ47" s="3">
         <v>80400</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2156000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2169000</v>
+      </c>
+      <c r="F48" s="3">
         <v>2157000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2185000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2215000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2149000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2159000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2217000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2337000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2350000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2354000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2388000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2409000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2421000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2369000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2315000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2272000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2220000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2138000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2116000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2081000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2031000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2007000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2004000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1974000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1876000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1844000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1293000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1244000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1205000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1104100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1075100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1019300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>993500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>991700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>937000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>939800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>924100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>821700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>816300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14993000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15053000</v>
+      </c>
+      <c r="F49" s="3">
         <v>13323000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>13352000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>13417000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>13461000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>13483000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>13570000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>13672000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>13736000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>13814000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>13893000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>13967000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>14054000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>14146000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>14236000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>14304000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>14451000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>14538000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>14488000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>13395000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>13500000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>13574000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>12101000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>12184000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>12230000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>12317000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>12411800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>12503700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>12615000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>12724800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>12650000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>7806300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>6144300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>6197600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>6207200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>6241300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>6242500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>6242800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>5820900</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5309,8 +5537,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5428,127 +5662,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1738000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1593000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1054000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1526000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1472000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1603000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1090000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1557000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1462000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1265000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>801000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1239000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1125000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>984000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1618000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1679000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1747000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1824000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1968000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2049000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1973000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2020000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2033000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>869000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>848000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>598000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>562700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>557100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>503200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>542900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>186500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>269100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>284200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>303400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>143500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>144600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>146100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>144300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5666,127 +5912,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29981000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>29933000</v>
+      </c>
+      <c r="F54" s="3">
         <v>29704000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29496000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>28754000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28107000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>29955000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>30230000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29830000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>30007000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>28751000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>29779000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>29090000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>27838000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>26667000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>27165000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>26744000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>26326000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>25976000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>27241000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>26144000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>25582000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>24985000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>24284000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>22414000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>21603000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>21214000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>20762400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>20054900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>19665900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>19505500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>18768700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>15395600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>15163400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>14973500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>14535600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>13906800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>13364900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>13044800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>12697200</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5828,8 +6086,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5871,186 +6131,194 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>529000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>499000</v>
+      </c>
+      <c r="F57" s="3">
         <v>419000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>417000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>337000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>360000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>326000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>361000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>318000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>357000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>300000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>314000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>314000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>346000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>308000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>379000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>316000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>366000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>295000</v>
-      </c>
-      <c r="U57" s="3">
-        <v>312000</v>
-      </c>
-      <c r="V57" s="3">
-        <v>331000</v>
       </c>
       <c r="W57" s="3">
         <v>312000</v>
       </c>
       <c r="X57" s="3">
+        <v>331000</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>312000</v>
+      </c>
+      <c r="Z57" s="3">
         <v>254000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>306000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>229000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>289000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>265000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>209500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>187000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>169100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>145300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>186300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>145600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>117200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>131100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>113500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>90300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>77900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>191500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1706000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1944000</v>
+      </c>
+      <c r="F58" s="3">
         <v>947000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>85000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>93000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>92000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>74000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1574000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1569000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1565000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1570000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>73000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>74000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>74000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>81000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>500000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>500000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>499000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>499000</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>10</v>
@@ -6058,11 +6326,11 @@
       <c r="X58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -6071,22 +6339,22 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
         <v>3149300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3148600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3145700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>892800</v>
-      </c>
-      <c r="AG58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>10</v>
@@ -6100,493 +6368,523 @@
       <c r="AL58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AM58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN58" s="3">
-        <v>0</v>
+      <c r="AM58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8029000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8002000</v>
+      </c>
+      <c r="F59" s="3">
         <v>8707000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7901000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>7421000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>7109000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>7549000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6994000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6016000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5758000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6205000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>6083000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6331000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5905000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5682000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>7249000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>6622000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>6520000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>6403000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>6620000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5860000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5833000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>5552000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>5206000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>4901000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>4875000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>4963000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>4832100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>4467400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>4372300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>4275700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>4114900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>3646500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>3611800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>3405400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>3413900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>3125800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>2970000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>2762600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>2723600</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11888000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12078000</v>
+      </c>
+      <c r="F60" s="3">
         <v>11390000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>10200000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>9239000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>9039000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>9163000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10521000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9644000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>9474000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>9537000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>8251000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8334000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8019000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7437000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>8128000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>7438000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>7385000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>7197000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>6932000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>6191000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>6145000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>5806000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>5512000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>5130000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>5164000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5228000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>8190900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>7803000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>7687100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>5313700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>4301100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>3792000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>3729000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>3536500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>3527500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>3216100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>3047900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>2954100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>2811600</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5081000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5133000</v>
+      </c>
+      <c r="F61" s="3">
         <v>5723000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6571000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6562000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6489000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6489000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4482000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4509000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4525000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2516000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4007000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4022000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4039000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4045000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3629000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>3627000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3627000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3626000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4123000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>4122000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>4120000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>4119000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>4117000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4116000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>4114000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>4113000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>988900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>988400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>987900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>3236800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>4124800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1874700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>1874100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>1874800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>1881400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>1889200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>1888400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>1884100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>1892200</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1138000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1063000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>977000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1034000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1017000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1065000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>994000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1005000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1037000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1103000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>890000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>850000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>826000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>859000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1357000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1306000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1329000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1378000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1389000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1417000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1465000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1514000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1391000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1455000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1444000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1408000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1052400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1020700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1059200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1083500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>980600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>867000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>854800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>928200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>666800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>631000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>624600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>618000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>568600</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6704,8 +7002,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6823,8 +7127,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6942,127 +7252,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18217000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18415000</v>
+      </c>
+      <c r="F66" s="3">
         <v>18271000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17873000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>16984000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>16659000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>16860000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>16125000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15285000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>15164000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13291000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>13261000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>13314000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13000000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12461000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>13114000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>12371000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>12341000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>12201000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>12444000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>11730000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>11730000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>11439000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>11020000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>10701000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>10722000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>10749000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>10232200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>9812100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>9734200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>9634100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>9406600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>6533700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>6457800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>6339500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>6075700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>5736400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>5560900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>5456100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>5272400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7104,8 +7426,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7223,8 +7547,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7342,8 +7672,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7461,8 +7797,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7580,127 +7922,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>50594000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>48767000</v>
+      </c>
+      <c r="F72" s="3">
         <v>47170000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>45354000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>43516000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>41744000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>40186000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>38470000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>36911000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>35227000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>33809000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>33346000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>32012000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>30609000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>29435000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>28319000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>27158000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>26022000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>24961000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>23905000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>22750000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>21538000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>20521000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>19611000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>17383000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>16428000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>15390000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>14828600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>13976700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>13183900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>12579300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>11815600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>11137400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>10471100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>9830400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>9573900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>9072300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>8652800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>8299400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>8114500</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7818,8 +8172,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7937,8 +8297,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8056,127 +8422,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11764000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11518000</v>
+      </c>
+      <c r="F76" s="3">
         <v>11433000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11623000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11770000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>11448000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13095000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14105000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14545000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>14843000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>15460000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>16518000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15776000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>14838000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14206000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>14051000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>14373000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>13985000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>13775000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14797000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>14414000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>13852000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>13546000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>13264000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>11713000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>10881000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>10465000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>10530200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>10242800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>9931700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>9871500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>9362100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>8861900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>8705600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>8634000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>8459900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>8170400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>7804000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>7588700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>7424800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8294,251 +8672,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46262</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46171</v>
+      </c>
+      <c r="F80" s="2">
         <v>46080</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45989</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45898</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45807</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45625</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45534</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45352</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45261</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45170</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45079</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44988</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44897</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44806</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44715</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44624</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44533</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44442</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44351</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44260</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44162</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44071</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43980</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43889</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43798</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43707</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43616</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43525</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43434</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43343</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43252</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43161</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43070</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42979</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42888</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42797</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42706</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1712000</v>
+      </c>
+      <c r="F81" s="3">
         <v>1889000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1856000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1772000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1691000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1811000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1683000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1684000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1573000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>620000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1483000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1403000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1295000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1247000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1176000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1136000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1178000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1266000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1233000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1212000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1116000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1261000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>2250000</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>955000</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>1100000</v>
       </c>
       <c r="AB81" s="3">
         <v>955000</v>
       </c>
       <c r="AC81" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>955000</v>
+      </c>
+      <c r="AE81" s="3">
         <v>851900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>792800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>632600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>674200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>678200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>666300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>663200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>583100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>501500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>419600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>374400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>398400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>399600</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8580,127 +8976,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>126000</v>
+      </c>
+      <c r="F83" s="3">
         <v>133000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>-54000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>129000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>130000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>128000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>-32000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>126000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>124000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>116000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>-23000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>115000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>111000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>112000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>215000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>216000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>212000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>213000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>205000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>193000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>194000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>196000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>190000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>191000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>188000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>188000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>295600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>150500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>145600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>144900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>106700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>86900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>76400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>76500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>81200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>82300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>81600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>80800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8818,8 +9222,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8937,8 +9347,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9056,8 +9472,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9175,8 +9597,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9294,127 +9722,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2523000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2165000</v>
+      </c>
+      <c r="F89" s="3">
         <v>2958000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3160000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2198000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2191000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2482000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2921000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2021000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1940000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1174000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1597000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1873000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2139000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1693000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2325000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1704000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2040000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1769000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2066000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1404000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1988000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1772000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1782000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1436000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1184000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1325000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1376400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>922600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1109300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1013400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1108000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>955300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>976400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>989600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>833200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>704400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>644800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>730400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>695600</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9456,127 +9896,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-37000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-34000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-72000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-47000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-26000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-48000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-57000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-41000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-37000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-47000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-91000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-121000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-91000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-125000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-126000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-100000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-99000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-95000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-95000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-103000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-126000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-96000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-94000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-94100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-89600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-145500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-65300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-62600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-63600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-45300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-95100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-37700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-54200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-48600</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9694,8 +10142,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9813,127 +10267,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-668000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1714000</v>
+      </c>
+      <c r="F94" s="3">
         <v>474000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-146000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-279000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-278000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-484000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>19000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-47000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>111000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>66000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>153000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>145000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>322000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>156000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-69000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-103000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-138000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-260000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1739000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-133000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-107000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1558000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-131000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-315000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>80000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-168400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-165300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>10100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-131900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-3138900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-1520300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>67700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-93800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>20400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-36800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-87500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-338900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-143100</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9975,8 +10441,10 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10019,11 +10487,11 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -10094,8 +10562,14 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10213,8 +10687,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10332,8 +10812,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10451,361 +10937,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2415000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1855000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2544000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2555000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1876000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-3788000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2841000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2501000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2453000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-642000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2128000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1217000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-871000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1080000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2014000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2604000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-899000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1080000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1244000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-940000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-414000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-901000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1233000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-765700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-624400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-772100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-783900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>1924700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-671700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-717400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-541300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-319500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-218300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-314400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-331500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-300500</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-12000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-19000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>7000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>21000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-36000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-26000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>21000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-36000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-26000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-10000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-28000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>16000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>1800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>6300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>8300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>5200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-560000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1413000</v>
+      </c>
+      <c r="F102" s="3">
         <v>901000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>449000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>51000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1827000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-855000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>420000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-467000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1406000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-887000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>540000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1145000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1384000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-164000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>366000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>505000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>626000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1105000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-779000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>373000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>798000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>711000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>723000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>356000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>38000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>441200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>126100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>344100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>96100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-104400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1240800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>321000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>360900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>531500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>457600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>248100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>57600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>243600</v>
       </c>
     </row>
